--- a/artfynd/A 18633-2022 artfynd.xlsx
+++ b/artfynd/A 18633-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118305345</v>
+        <v>118305352</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>100107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484662</v>
+        <v>484691</v>
       </c>
       <c r="R2" t="n">
-        <v>6473831</v>
+        <v>6473673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118305347</v>
+        <v>118305345</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>57993</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484611</v>
+        <v>484662</v>
       </c>
       <c r="R3" t="n">
-        <v>6473826</v>
+        <v>6473831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118305352</v>
+        <v>118305347</v>
       </c>
       <c r="B4" t="n">
         <v>100107</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484691</v>
+        <v>484611</v>
       </c>
       <c r="R4" t="n">
-        <v>6473673</v>
+        <v>6473826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18633-2022 artfynd.xlsx
+++ b/artfynd/A 18633-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118305352</v>
+        <v>118305345</v>
       </c>
       <c r="B2" t="n">
-        <v>100107</v>
+        <v>57993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484691</v>
+        <v>484662</v>
       </c>
       <c r="R2" t="n">
-        <v>6473673</v>
+        <v>6473831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118305345</v>
+        <v>118305347</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>100107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484662</v>
+        <v>484611</v>
       </c>
       <c r="R3" t="n">
-        <v>6473831</v>
+        <v>6473826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118305347</v>
+        <v>118305352</v>
       </c>
       <c r="B4" t="n">
         <v>100107</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484611</v>
+        <v>484691</v>
       </c>
       <c r="R4" t="n">
-        <v>6473826</v>
+        <v>6473673</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18633-2022 artfynd.xlsx
+++ b/artfynd/A 18633-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118305345</v>
+        <v>118305352</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>100114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484662</v>
+        <v>484691</v>
       </c>
       <c r="R2" t="n">
-        <v>6473831</v>
+        <v>6473673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
         <v>118305347</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118305352</v>
+        <v>118305345</v>
       </c>
       <c r="B4" t="n">
-        <v>100107</v>
+        <v>57993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484691</v>
+        <v>484662</v>
       </c>
       <c r="R4" t="n">
-        <v>6473673</v>
+        <v>6473831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18633-2022 artfynd.xlsx
+++ b/artfynd/A 18633-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118305352</v>
+        <v>118305348</v>
       </c>
       <c r="B2" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484691</v>
+        <v>484666</v>
       </c>
       <c r="R2" t="n">
-        <v>6473673</v>
+        <v>6473631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118305347</v>
+        <v>118305345</v>
       </c>
       <c r="B3" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484611</v>
+        <v>484662</v>
       </c>
       <c r="R3" t="n">
-        <v>6473826</v>
+        <v>6473831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118305345</v>
+        <v>118305347</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484662</v>
+        <v>484611</v>
       </c>
       <c r="R4" t="n">
-        <v>6473831</v>
+        <v>6473826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +975,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118305352</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grönlund, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484691</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6473673</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vadstena</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rogslösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Valdemar Mejstad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18633-2022 artfynd.xlsx
+++ b/artfynd/A 18633-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118305348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118305345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118305347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118305352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>